--- a/reports/2026-09_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
+++ b/reports/2026-09_月次実績報告/excel/第51期下期広域営業部担当者別実績.xlsx
@@ -28071,7 +28071,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>6727</v>
+        <v>6727.123</v>
       </c>
       <c r="F85" s="4" t="n">
         <v>4624.074</v>
@@ -28323,7 +28323,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>5089</v>
+        <v>5088.679</v>
       </c>
       <c r="F88" s="4" t="n">
         <v>3321.006</v>
@@ -28345,7 +28345,7 @@
         <v/>
       </c>
       <c r="L88" s="3" t="n">
-        <v>618</v>
+        <v>618.2190000000001</v>
       </c>
       <c r="M88" s="4" t="n">
         <v>409.916</v>
@@ -28354,7 +28354,7 @@
         <v>510.338</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>930.6950000000001</v>
+        <v>822.485</v>
       </c>
       <c r="P88" s="4" t="n">
         <v>712.8835</v>
